--- a/정기/리소스정리/리소스메니저 작업중.xlsx
+++ b/정기/리소스정리/리소스메니저 작업중.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\리소스정리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C61239-2835-4271-890B-C9D1AED466CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4235E239-B0B8-45D2-83D5-ACFC26AC221D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38355" yWindow="0" windowWidth="18570" windowHeight="15480" xr2:uid="{1D1919E6-8750-49D2-A825-2B8010F1E320}"/>
+    <workbookView xWindow="7950" yWindow="240" windowWidth="30600" windowHeight="15480" xr2:uid="{1D1919E6-8750-49D2-A825-2B8010F1E320}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="단위 환산" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="240">
   <si>
     <t>리소스 이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -510,6 +511,276 @@
   </si>
   <si>
     <t>현무의갑옷</t>
+  </si>
+  <si>
+    <t>1A   100만</t>
+  </si>
+  <si>
+    <t>10A   1000만</t>
+  </si>
+  <si>
+    <t>100A   1억</t>
+  </si>
+  <si>
+    <t>1B   10억</t>
+  </si>
+  <si>
+    <t>10B   100억</t>
+  </si>
+  <si>
+    <t>100B   1000억</t>
+  </si>
+  <si>
+    <t>1C   1조</t>
+  </si>
+  <si>
+    <t>10C   10조</t>
+  </si>
+  <si>
+    <t>100C   100조</t>
+  </si>
+  <si>
+    <t>1D        1000조</t>
+  </si>
+  <si>
+    <t>10D      1경</t>
+  </si>
+  <si>
+    <t>100D    10경</t>
+  </si>
+  <si>
+    <t>1E         100경</t>
+  </si>
+  <si>
+    <t>10E       1000경</t>
+  </si>
+  <si>
+    <t>100E     1해</t>
+  </si>
+  <si>
+    <t>1F         10해</t>
+  </si>
+  <si>
+    <t>10F       100해</t>
+  </si>
+  <si>
+    <t>100F     1000해</t>
+  </si>
+  <si>
+    <t>1G        1자</t>
+  </si>
+  <si>
+    <t>10G      10자</t>
+  </si>
+  <si>
+    <t>100G    100자</t>
+  </si>
+  <si>
+    <t>1H        1000자</t>
+  </si>
+  <si>
+    <t>10H      1양</t>
+  </si>
+  <si>
+    <t>100H    10양</t>
+  </si>
+  <si>
+    <t>1I          100양</t>
+  </si>
+  <si>
+    <t>10I        1000양</t>
+  </si>
+  <si>
+    <t>I00I       1구</t>
+  </si>
+  <si>
+    <t>1J          10구</t>
+  </si>
+  <si>
+    <t>10J        100구</t>
+  </si>
+  <si>
+    <t>100J      1000구</t>
+  </si>
+  <si>
+    <t>1K         1간</t>
+  </si>
+  <si>
+    <t>10K       10간</t>
+  </si>
+  <si>
+    <t>100K     100간</t>
+  </si>
+  <si>
+    <t>1L         1000간</t>
+  </si>
+  <si>
+    <t>10L       1정</t>
+  </si>
+  <si>
+    <t>100L     10정</t>
+  </si>
+  <si>
+    <t>1M       100정</t>
+  </si>
+  <si>
+    <t>10M     1000정</t>
+  </si>
+  <si>
+    <t>100M    1재</t>
+  </si>
+  <si>
+    <t>1N        10재</t>
+  </si>
+  <si>
+    <t>10N      100재</t>
+  </si>
+  <si>
+    <t>100N    1000재</t>
+  </si>
+  <si>
+    <t>1O        1극</t>
+  </si>
+  <si>
+    <t>10O      10극</t>
+  </si>
+  <si>
+    <t>100O    100극</t>
+  </si>
+  <si>
+    <t>1P         1000극</t>
+  </si>
+  <si>
+    <t>10P       1항하사</t>
+  </si>
+  <si>
+    <t>100P     10항하사</t>
+  </si>
+  <si>
+    <t>1Q        100항하사</t>
+  </si>
+  <si>
+    <t>10Q      1000항하사</t>
+  </si>
+  <si>
+    <t>100Q    1아승기</t>
+  </si>
+  <si>
+    <t>1R         10아승기</t>
+  </si>
+  <si>
+    <t>10R       100아승기</t>
+  </si>
+  <si>
+    <t>100R     1000아승기</t>
+  </si>
+  <si>
+    <t>1S         1나유타</t>
+  </si>
+  <si>
+    <t>10S       10나유타</t>
+  </si>
+  <si>
+    <t>100S     100나유타</t>
+  </si>
+  <si>
+    <t>1T         1000나유타</t>
+  </si>
+  <si>
+    <t>10T       1불가사의</t>
+  </si>
+  <si>
+    <t>100T     10불가사의</t>
+  </si>
+  <si>
+    <t>1U        100불가사의</t>
+  </si>
+  <si>
+    <t>10U      1000불가사의</t>
+  </si>
+  <si>
+    <t>100U    1무량수/무량대수</t>
+  </si>
+  <si>
+    <t>1V        10무량수/무량대수</t>
+  </si>
+  <si>
+    <t>10V      100무량수/무량대수</t>
+  </si>
+  <si>
+    <t>100V    1000무량수/무량대수</t>
+  </si>
+  <si>
+    <t>1W       1대수</t>
+  </si>
+  <si>
+    <t>10W     10대수</t>
+  </si>
+  <si>
+    <t>100W   100대수</t>
+  </si>
+  <si>
+    <t>1X        1000대수     10의71승</t>
+  </si>
+  <si>
+    <t>10X      1대수2         10의72승</t>
+  </si>
+  <si>
+    <t>100X</t>
+  </si>
+  <si>
+    <t>1Y</t>
+  </si>
+  <si>
+    <t>10Y</t>
+  </si>
+  <si>
+    <t>100Y</t>
+  </si>
+  <si>
+    <t>1Z</t>
+  </si>
+  <si>
+    <t>10Z</t>
+  </si>
+  <si>
+    <t>100Z</t>
+  </si>
+  <si>
+    <t>이벤트코인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요괴전재화1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요괴전재화2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요괴전재화3</t>
+  </si>
+  <si>
+    <t>요괴전재화4</t>
+  </si>
+  <si>
+    <t>요괴전재화5</t>
+  </si>
+  <si>
+    <t>요괴전재화6</t>
+  </si>
+  <si>
+    <t>요괴전재화7</t>
+  </si>
+  <si>
+    <t>요괴전재화8</t>
+  </si>
+  <si>
+    <t>요괴전재화9</t>
+  </si>
+  <si>
+    <t>요괴전재화10</t>
   </si>
 </sst>
 </file>
@@ -533,20 +804,57 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -555,8 +863,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -893,7 +1210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70BC40E3-2E8F-494A-BAC5-1ADBE2A23229}">
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D156"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
@@ -1095,169 +1412,169 @@
         <v>96</v>
       </c>
     </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>96</v>
+      </c>
+    </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>231</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>232</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>233</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="C25">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26">
-        <v>10</v>
-      </c>
-      <c r="D26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
         <v>98</v>
       </c>
       <c r="C27">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D27" t="s">
         <v>95</v>
@@ -1265,13 +1582,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
         <v>98</v>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D28" t="s">
         <v>95</v>
@@ -1279,13 +1596,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
         <v>98</v>
       </c>
       <c r="C29">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D29" t="s">
         <v>95</v>
@@ -1293,13 +1610,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
         <v>98</v>
       </c>
       <c r="C30">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D30" t="s">
         <v>95</v>
@@ -1307,13 +1624,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B31" t="s">
         <v>98</v>
       </c>
       <c r="C31">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D31" t="s">
         <v>95</v>
@@ -1321,13 +1638,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B32" t="s">
         <v>98</v>
       </c>
       <c r="C32">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D32" t="s">
         <v>95</v>
@@ -1335,13 +1652,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
         <v>98</v>
       </c>
       <c r="C33">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D33" t="s">
         <v>95</v>
@@ -1349,13 +1666,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
         <v>98</v>
       </c>
       <c r="C34">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D34" t="s">
         <v>95</v>
@@ -1363,13 +1680,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
         <v>98</v>
       </c>
       <c r="C35">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D35" t="s">
         <v>95</v>
@@ -1377,13 +1694,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B36" t="s">
         <v>98</v>
       </c>
       <c r="C36">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D36" t="s">
         <v>95</v>
@@ -1391,13 +1708,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
         <v>98</v>
       </c>
       <c r="C37">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D37" t="s">
         <v>95</v>
@@ -1405,13 +1722,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
         <v>98</v>
       </c>
       <c r="C38">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D38" t="s">
         <v>95</v>
@@ -1419,13 +1736,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
         <v>98</v>
       </c>
       <c r="C39">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D39" t="s">
         <v>95</v>
@@ -1433,13 +1750,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
         <v>98</v>
       </c>
       <c r="C40">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
         <v>95</v>
@@ -1447,13 +1764,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B41" t="s">
         <v>98</v>
       </c>
       <c r="C41">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
         <v>95</v>
@@ -1461,13 +1778,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s">
         <v>98</v>
       </c>
       <c r="C42">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D42" t="s">
         <v>95</v>
@@ -1475,13 +1792,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B43" t="s">
         <v>98</v>
       </c>
       <c r="C43">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D43" t="s">
         <v>95</v>
@@ -1489,13 +1806,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
         <v>98</v>
       </c>
       <c r="C44">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D44" t="s">
         <v>95</v>
@@ -1503,13 +1820,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B45" t="s">
         <v>98</v>
       </c>
       <c r="C45">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
         <v>95</v>
@@ -1517,13 +1834,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
         <v>98</v>
       </c>
       <c r="C46">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D46" t="s">
         <v>95</v>
@@ -1531,13 +1848,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B47" t="s">
         <v>98</v>
       </c>
       <c r="C47">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D47" t="s">
         <v>95</v>
@@ -1545,13 +1862,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B48" t="s">
         <v>98</v>
       </c>
       <c r="C48">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D48" t="s">
         <v>95</v>
@@ -1559,13 +1876,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B49" t="s">
         <v>98</v>
       </c>
       <c r="C49">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D49" t="s">
         <v>95</v>
@@ -1573,13 +1890,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B50" t="s">
         <v>98</v>
       </c>
       <c r="C50">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D50" t="s">
         <v>95</v>
@@ -1587,13 +1904,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
         <v>98</v>
       </c>
       <c r="C51">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D51" t="s">
         <v>95</v>
@@ -1601,13 +1918,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
         <v>98</v>
       </c>
       <c r="C52">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D52" t="s">
         <v>95</v>
@@ -1615,13 +1932,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B53" t="s">
         <v>98</v>
       </c>
       <c r="C53">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D53" t="s">
         <v>95</v>
@@ -1629,13 +1946,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B54" t="s">
         <v>98</v>
       </c>
       <c r="C54">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D54" t="s">
         <v>95</v>
@@ -1643,13 +1960,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B55" t="s">
         <v>98</v>
       </c>
       <c r="C55">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D55" t="s">
         <v>95</v>
@@ -1657,13 +1974,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B56" t="s">
         <v>98</v>
       </c>
       <c r="C56">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D56" t="s">
         <v>95</v>
@@ -1671,13 +1988,13 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B57" t="s">
         <v>98</v>
       </c>
       <c r="C57">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D57" t="s">
         <v>95</v>
@@ -1685,13 +2002,13 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B58" t="s">
         <v>98</v>
       </c>
       <c r="C58">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D58" t="s">
         <v>95</v>
@@ -1699,13 +2016,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B59" t="s">
         <v>98</v>
       </c>
       <c r="C59">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D59" t="s">
         <v>95</v>
@@ -1713,13 +2030,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B60" t="s">
         <v>98</v>
       </c>
       <c r="C60">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D60" t="s">
         <v>95</v>
@@ -1727,13 +2044,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B61" t="s">
         <v>98</v>
       </c>
       <c r="C61">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D61" t="s">
         <v>95</v>
@@ -1741,13 +2058,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B62" t="s">
         <v>98</v>
       </c>
       <c r="C62">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D62" t="s">
         <v>95</v>
@@ -1755,13 +2072,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B63" t="s">
         <v>98</v>
       </c>
       <c r="C63">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D63" t="s">
         <v>95</v>
@@ -1769,13 +2086,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B64" t="s">
         <v>98</v>
       </c>
       <c r="C64">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D64" t="s">
         <v>95</v>
@@ -1783,13 +2100,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B65" t="s">
         <v>98</v>
       </c>
       <c r="C65">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D65" t="s">
         <v>95</v>
@@ -1797,13 +2114,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B66" t="s">
         <v>98</v>
       </c>
       <c r="C66">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D66" t="s">
         <v>95</v>
@@ -1811,13 +2128,13 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B67" t="s">
         <v>98</v>
       </c>
       <c r="C67">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D67" t="s">
         <v>95</v>
@@ -1825,13 +2142,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B68" t="s">
         <v>98</v>
       </c>
       <c r="C68">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D68" t="s">
         <v>95</v>
@@ -1839,13 +2156,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B69" t="s">
         <v>98</v>
       </c>
       <c r="C69">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D69" t="s">
         <v>95</v>
@@ -1853,13 +2170,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B70" t="s">
         <v>98</v>
       </c>
       <c r="C70">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D70" t="s">
         <v>95</v>
@@ -1867,13 +2184,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B71" t="s">
         <v>98</v>
       </c>
       <c r="C71">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D71" t="s">
         <v>95</v>
@@ -1881,13 +2198,13 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B72" t="s">
         <v>98</v>
       </c>
       <c r="C72">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D72" t="s">
         <v>95</v>
@@ -1895,424 +2212,457 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B73" t="s">
         <v>98</v>
       </c>
       <c r="C73">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D73" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>68</v>
+      </c>
+      <c r="B74" t="s">
+        <v>98</v>
+      </c>
+      <c r="C74">
+        <v>47</v>
+      </c>
+      <c r="D74" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="B75" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D75" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B76" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B77" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D77" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>72</v>
+      </c>
+      <c r="B78" t="s">
+        <v>98</v>
+      </c>
+      <c r="C78">
+        <v>51</v>
+      </c>
+      <c r="D78" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B79" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D79" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B80" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="D80" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B81" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="D81" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B82" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="D82" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C83">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="D83" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B84" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C84">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="D84" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>86</v>
-      </c>
-      <c r="B85" t="s">
-        <v>87</v>
-      </c>
-      <c r="C85">
-        <v>6</v>
-      </c>
-      <c r="D85" t="s">
-        <v>93</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>91</v>
+      </c>
+      <c r="B86" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="B87" t="s">
+        <v>79</v>
+      </c>
+      <c r="C87">
         <v>1</v>
       </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
       <c r="D87" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>4</v>
-      </c>
-      <c r="B89" t="s">
-        <v>1</v>
-      </c>
-      <c r="C89">
-        <v>2</v>
-      </c>
-      <c r="D89" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="B90" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="C90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="B91" t="s">
+        <v>87</v>
+      </c>
+      <c r="C91">
         <v>1</v>
       </c>
-      <c r="C91">
+      <c r="D91" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>82</v>
+      </c>
+      <c r="B92" t="s">
+        <v>87</v>
+      </c>
+      <c r="C92">
+        <v>2</v>
+      </c>
+      <c r="D92" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>83</v>
+      </c>
+      <c r="B93" t="s">
+        <v>87</v>
+      </c>
+      <c r="C93">
+        <v>3</v>
+      </c>
+      <c r="D93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>84</v>
+      </c>
+      <c r="B94" t="s">
+        <v>87</v>
+      </c>
+      <c r="C94">
         <v>4</v>
       </c>
-      <c r="D91" t="s">
-        <v>92</v>
+      <c r="D94" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="B95" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="D95" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="B96" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C96">
+        <v>6</v>
+      </c>
+      <c r="D96" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>2</v>
+      </c>
+      <c r="B98" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>124</v>
-      </c>
-      <c r="B97" t="s">
-        <v>101</v>
-      </c>
-      <c r="C97">
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>4</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1</v>
+      </c>
+      <c r="C100">
         <v>2</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>124</v>
-      </c>
-      <c r="B98" t="s">
-        <v>102</v>
-      </c>
-      <c r="C98">
+      <c r="D100" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>5</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1</v>
+      </c>
+      <c r="C101">
         <v>3</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>124</v>
-      </c>
-      <c r="B99" t="s">
-        <v>103</v>
-      </c>
-      <c r="C99">
+      <c r="D101" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>6</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1</v>
+      </c>
+      <c r="C102">
         <v>4</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>124</v>
-      </c>
-      <c r="B100" t="s">
-        <v>104</v>
-      </c>
-      <c r="C100">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>124</v>
-      </c>
-      <c r="B101" t="s">
-        <v>105</v>
-      </c>
-      <c r="C101">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>124</v>
-      </c>
-      <c r="B102" t="s">
-        <v>106</v>
-      </c>
-      <c r="C102">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>124</v>
-      </c>
-      <c r="B103" t="s">
-        <v>107</v>
-      </c>
-      <c r="C103">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>124</v>
-      </c>
-      <c r="B104" t="s">
-        <v>108</v>
-      </c>
-      <c r="C104">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>124</v>
-      </c>
-      <c r="B105" t="s">
-        <v>109</v>
-      </c>
-      <c r="C105">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D102" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>124</v>
       </c>
       <c r="B106" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C106">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>124</v>
       </c>
       <c r="B107" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C107">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>124</v>
       </c>
       <c r="B108" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C108">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>124</v>
       </c>
       <c r="B109" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C109">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>124</v>
       </c>
       <c r="B110" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C110">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>124</v>
       </c>
       <c r="B111" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C111">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>124</v>
       </c>
       <c r="B112" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C112">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -2320,10 +2670,10 @@
         <v>124</v>
       </c>
       <c r="B113" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C113">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -2331,10 +2681,10 @@
         <v>124</v>
       </c>
       <c r="B114" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C114">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
@@ -2342,10 +2692,10 @@
         <v>124</v>
       </c>
       <c r="B115" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C115">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
@@ -2353,10 +2703,10 @@
         <v>124</v>
       </c>
       <c r="B116" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C116">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -2364,10 +2714,10 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C117">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -2375,10 +2725,10 @@
         <v>124</v>
       </c>
       <c r="B118" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C118">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -2386,131 +2736,131 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C119">
-        <v>24</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>124</v>
+      </c>
+      <c r="B120" t="s">
+        <v>113</v>
+      </c>
+      <c r="C120">
+        <v>14</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B121" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B122" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C123">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B124" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C124">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C125">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C126">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C127">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B129" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C129">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B130" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="C130">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>125</v>
-      </c>
-      <c r="B131" t="s">
-        <v>136</v>
-      </c>
-      <c r="C131">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -2518,10 +2868,10 @@
         <v>125</v>
       </c>
       <c r="B132" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C132">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -2529,10 +2879,10 @@
         <v>125</v>
       </c>
       <c r="B133" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C133">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
@@ -2540,10 +2890,10 @@
         <v>125</v>
       </c>
       <c r="B134" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C134">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
@@ -2551,10 +2901,10 @@
         <v>125</v>
       </c>
       <c r="B135" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C135">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
@@ -2562,10 +2912,10 @@
         <v>125</v>
       </c>
       <c r="B136" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C136">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
@@ -2573,10 +2923,10 @@
         <v>125</v>
       </c>
       <c r="B137" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="C137">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
@@ -2584,10 +2934,10 @@
         <v>125</v>
       </c>
       <c r="B138" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C138">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
@@ -2595,10 +2945,10 @@
         <v>125</v>
       </c>
       <c r="B139" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C139">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
@@ -2606,10 +2956,10 @@
         <v>125</v>
       </c>
       <c r="B140" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C140">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
@@ -2617,10 +2967,10 @@
         <v>125</v>
       </c>
       <c r="B141" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C141">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
@@ -2628,10 +2978,10 @@
         <v>125</v>
       </c>
       <c r="B142" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C142">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
@@ -2639,10 +2989,10 @@
         <v>125</v>
       </c>
       <c r="B143" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C143">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
@@ -2650,10 +3000,10 @@
         <v>125</v>
       </c>
       <c r="B144" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C144">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
@@ -2661,10 +3011,844 @@
         <v>125</v>
       </c>
       <c r="B145" t="s">
+        <v>139</v>
+      </c>
+      <c r="C145">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>125</v>
+      </c>
+      <c r="B146" t="s">
+        <v>140</v>
+      </c>
+      <c r="C146">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>125</v>
+      </c>
+      <c r="B147" t="s">
+        <v>141</v>
+      </c>
+      <c r="C147">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>125</v>
+      </c>
+      <c r="B148" t="s">
+        <v>142</v>
+      </c>
+      <c r="C148">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>125</v>
+      </c>
+      <c r="B149" t="s">
+        <v>143</v>
+      </c>
+      <c r="C149">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>125</v>
+      </c>
+      <c r="B150" t="s">
+        <v>144</v>
+      </c>
+      <c r="C150">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>125</v>
+      </c>
+      <c r="B151" t="s">
+        <v>145</v>
+      </c>
+      <c r="C151">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>125</v>
+      </c>
+      <c r="B152" t="s">
+        <v>146</v>
+      </c>
+      <c r="C152">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>125</v>
+      </c>
+      <c r="B153" t="s">
+        <v>147</v>
+      </c>
+      <c r="C153">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>125</v>
+      </c>
+      <c r="B154" t="s">
+        <v>148</v>
+      </c>
+      <c r="C154">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>125</v>
+      </c>
+      <c r="B155" t="s">
+        <v>149</v>
+      </c>
+      <c r="C155">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>125</v>
+      </c>
+      <c r="B156" t="s">
         <v>150</v>
       </c>
-      <c r="C145">
+      <c r="C156">
         <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96DCCA7B-F711-410D-B1AA-F02CC54C58CC}">
+  <dimension ref="A1:H78"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="1">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="2">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="2">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="2">
+        <v>10000000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="2">
+        <v>100000000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1000000000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" s="2">
+        <v>10000000000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="3">
+        <v>100000000000000</v>
+      </c>
+      <c r="H9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="2">
+        <f>C9*10</f>
+        <v>1000000000000000</v>
+      </c>
+      <c r="H10">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="2">
+        <f t="shared" ref="C11:C74" si="0">C10*10</f>
+        <v>1E+16</v>
+      </c>
+      <c r="H11">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" si="0"/>
+        <v>1E+17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" s="2">
+        <f t="shared" si="0"/>
+        <v>1E+18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" s="2">
+        <f t="shared" si="0"/>
+        <v>1E+19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" s="2">
+        <f t="shared" si="0"/>
+        <v>1E+20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" s="2">
+        <f t="shared" si="0"/>
+        <v>1E+21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="2">
+        <f t="shared" si="0"/>
+        <v>1E+22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C18" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999992E+22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999998E+23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999988E+24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999988E+25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>172</v>
+      </c>
+      <c r="C22" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999988E+26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>173</v>
+      </c>
+      <c r="C23" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999996E+27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>174</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999991E+28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>175</v>
+      </c>
+      <c r="C25" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999988E+29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999985E+30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999987E+31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>178</v>
+      </c>
+      <c r="C28" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999995E+32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>179</v>
+      </c>
+      <c r="C29" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999995E+33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>180</v>
+      </c>
+      <c r="C30" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999997E+34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999989E+35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999984E+36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>183</v>
+      </c>
+      <c r="C33" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999979E+37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>184</v>
+      </c>
+      <c r="C34" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999979E+38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>185</v>
+      </c>
+      <c r="C35" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999979E+39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>186</v>
+      </c>
+      <c r="C36" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999981E+40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>187</v>
+      </c>
+      <c r="C37" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999989E+41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>188</v>
+      </c>
+      <c r="C38" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999989E+42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>189</v>
+      </c>
+      <c r="C39" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999989E+43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>190</v>
+      </c>
+      <c r="C40" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999993E+44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>191</v>
+      </c>
+      <c r="C41" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999999E+45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>192</v>
+      </c>
+      <c r="C42" s="2">
+        <f t="shared" si="0"/>
+        <v>1E+47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>193</v>
+      </c>
+      <c r="C43" s="2">
+        <f t="shared" si="0"/>
+        <v>1E+48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>194</v>
+      </c>
+      <c r="C44" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>195</v>
+      </c>
+      <c r="C45" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>196</v>
+      </c>
+      <c r="C46" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999999E+50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>197</v>
+      </c>
+      <c r="C47" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999999E+51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>198</v>
+      </c>
+      <c r="C48" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999999E+52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>199</v>
+      </c>
+      <c r="C49" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+54</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>200</v>
+      </c>
+      <c r="C50" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>201</v>
+      </c>
+      <c r="C51" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>202</v>
+      </c>
+      <c r="C52" s="2">
+        <f t="shared" si="0"/>
+        <v>1E+57</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>203</v>
+      </c>
+      <c r="C53" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>204</v>
+      </c>
+      <c r="C54" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+59</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>205</v>
+      </c>
+      <c r="C55" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>206</v>
+      </c>
+      <c r="C56" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>207</v>
+      </c>
+      <c r="C57" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+62</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000002E+63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>209</v>
+      </c>
+      <c r="C59" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000002E+64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>210</v>
+      </c>
+      <c r="C60" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000002E+65</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>211</v>
+      </c>
+      <c r="C61" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>212</v>
+      </c>
+      <c r="C62" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+67</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>213</v>
+      </c>
+      <c r="C63" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+68</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>214</v>
+      </c>
+      <c r="C64" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+69</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>215</v>
+      </c>
+      <c r="C65" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+70</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>216</v>
+      </c>
+      <c r="C66" s="2">
+        <f t="shared" si="0"/>
+        <v>1E+71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>217</v>
+      </c>
+      <c r="C67" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>218</v>
+      </c>
+      <c r="C68" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+73</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>219</v>
+      </c>
+      <c r="C69" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>220</v>
+      </c>
+      <c r="C70" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>221</v>
+      </c>
+      <c r="C71" s="2">
+        <f t="shared" si="0"/>
+        <v>1E+76</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>222</v>
+      </c>
+      <c r="C72" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+77</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>223</v>
+      </c>
+      <c r="C73" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000002E+78</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>224</v>
+      </c>
+      <c r="C74" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000001E+79</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>225</v>
+      </c>
+      <c r="C75" s="2">
+        <f t="shared" ref="C75:C78" si="1">C74*10</f>
+        <v>1.0000000000000001E+80</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>226</v>
+      </c>
+      <c r="C76" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000001E+81</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>227</v>
+      </c>
+      <c r="C77" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000001E+82</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>228</v>
+      </c>
+      <c r="C78" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000002E+83</v>
       </c>
     </row>
   </sheetData>
